--- a/output_excel/17176277.xlsx
+++ b/output_excel/17176277.xlsx
@@ -571,7 +571,7 @@
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>1x3x120(70)AX | V7-8 | BT | 3x70AX(5AZN) | MT | 38.08M | 240.23M | 112,5KVA | 37,5KVA | 112,5KVA | 112,5KVA | 37,5KVA | CONEX. | 71 | AVENIDA | 3x336AN | 37,5KVA | BT | DG | 30.74M | 112,5KVA | 3x336AN | 112,5KVA | FERRAGEM | 400816F | 112,5KVA | CAMPO | CAMPO</t>
+          <t>1x3x120(70)AX | BT | 3x70AX(5AZN) | MT | 38.08M | 240.23M</t>
         </is>
       </c>
       <c r="I2" s="3" t="n">
@@ -608,19 +608,27 @@
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>12m</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM | (DCIM) | P7x | DG | 5M | BT | V7-8 | MT | 3M | 20M | BF-A | V6-7 | BF-A | BF-A | 1x3x120(70)AX | 3x70AX(5AZN) | BF-A | 30K | (DCIM) | 3x336AN | BT | 112,5KVA | CONEX. | Q/R | 112,5KVA | 1x3x120(70)AX | QX16 | DG | (DCIM) | BF-A | 112,5KVA | 30K | 30K | (DCIM) | 112,5KVA | TX10 | CONEX. | 112,5KVA | MT | QX10 | Q/R | 112,5KVA | FERRAGEM | BF-A | 3x70AX(5AZN)</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
+          <t>FERRAGEM | (DCIM) | DG | 20M | 3M | 6 | BF-A | 1 | 3 | CONEX. | (DCIM) | Q/R | BF-A | 1 | BF-A | 5M | BT | BF-A | MT | 0 | BF-A | 1 | 2 | DG | CONEX. | 0 | (DCIM) | Q/R | 1 | 1x3x120(70)AX | BF-A | 6 | 1 | 1 | 0 | CONEX. | (DCIM) | BT | 1 | TX10 | 3x70AX(5AZN) | QX16 | QX10 | 2 | 1 | SMTG112,5KVAL1(1) | C12X300112,5KVACEAFS112,5KVA1AF(1)112,5KVAIP | CONEX. | 1</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -657,7 +665,7 @@
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1x3x120(70)AX | BT | 3x70AX(5AZN) | V6-7 | MT | 30.74M | 30.74M | P7x | MT | 3x70AX(5AZN) | DG | (DCIM) | BT | FERRAGEM | 1x3x120(70)AX | 33.59M | 5M</t>
+          <t>MT | 3x70AX(5AZN) | BT | 1x3x120(70)AX | 30.74M</t>
         </is>
       </c>
       <c r="I4" s="3" t="n">
@@ -706,7 +714,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>(DCIM) | FERRAGEM | 5M | BF-A | P6 | QX16 | 112,5KVA | BF-A | DG | L5 | 3M | P7x | BF-A | B4M | 25M | 20M | BF-A | LC | BF-A | BF-A | QX10 | V6-7 | 112,5KVA | BT | MT | TX10 | 112,5KVA | FERRAGEM | (DCIM) | 1x3x120(70)AX | QX10 | 3x70AX(5AZN) | QX16 | RAMAL | C12X300112,5KVACEAFS112,5KVA1AF(1)112,5KVAIP | 112,5KVA | C12X300112,5KVACEAFS112,5KVA1AF(1)112,5KVAIP | SMTG112,5KVAL1(1) | 112,5KVA | 112,5KVA | V5-6</t>
+          <t>DG | 5M | (DCIM) | BF-A | FERRAGEM | QX16 | BT | FERRAGEM | 3M | (DCIM) | 1 | MT | BF-A | BF-A | 1x3x120(70)AX | 20M | BF-A | 3x70AX(5AZN) | L5 | QX10 | TX10 | 1 | 2 | 4M | C12X300112,5KVACEAFS112,5KVA1AF(1)112,5KVAIP | 25M</t>
         </is>
       </c>
       <c r="I5" s="4" t="n">
@@ -751,7 +759,7 @@
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1x3x120(70)AX | BT | V5-6 | 3x70AX(5AZN) | MT | GD | 33.59M | 33.59M | BM | P6 | MT</t>
+          <t>1x3x120(70)AX | BT | 3x70AX(5AZN) | MT | GD | 33.59M | 33.59M</t>
         </is>
       </c>
       <c r="I6" s="3" t="n">
@@ -800,7 +808,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>P5 | BM | ANCORAR | CAMINHÃO | CALÇADA | (KL) | 112,5KVA | 112,5KVA | (KL) | BT | 112,5KVA | AVENIDA | 566993 | FERRAGEM | CLANDESTINOS: | 3x336AN | AVENIDA | (DCIM) | ANCORAR | 175ET005296879 | 112,5KVA | MV | AVENIDA | 3x336AN | (KL) | GD | ANCORAR | ANCORAR | (DCIM) | 75KVA | AVENIDA | V4-5 | 112,5KVA | (DCIM) | 13200 | C10x600,B1M,M3F | REAPROVEITAR | BF-A | RAMAL | 112,5KVA | LC | MT</t>
+          <t>BM | ANCORAR | CAMINHÃO | (KL) | CALÇADA | 112,5KVA | 112,5KVA | BT | 566993 | (KL) | AVENIDA | 112,5KVA | FERRAGEM | MV | GD | CLANDESTINOS: | LC | AVENIDA | 3x336AN | 175ET005296879 | RAMAL | (DCIM) | 2 | ANCORAR | 25M | BF-A | 112,5KVA | AVENIDA | QX16 | BT | MT | 2 | 3x336AN | (KL) | 75KVA | 4M | BF-A | QX10 | ANCORAR | 1 | ANCORAR | 1x3x120(70)AX | 3x70AX(5AZN) | 13200 | C10x600,B1M,M3F</t>
         </is>
       </c>
       <c r="I7" s="4" t="n">
@@ -849,7 +857,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>P4-30 | CABOS | ANCORAR | 3x336AN | 58M | 112,5KVA | BF-A | RAMAIS | B1F | CABOS | ANCORAR | TX16 | (DCIM) | 1x2x4AC | V4-5 | BT | C12X300112,5KVACE1112,5KVAIP | AV. | MT | SMTG112,5KVAL1(2) | BT | 1x3x120(70)AX | 3x70AX(5AZN) | 112,5KVA | (KL) | 112,5KVA | CLANDESTINOS: | CALÇADA | 3x336AN | (DCIM) | CAMINHÃO | 112,5KVA | ANCORAR | 3x336AN | ANCORAR | (DCIM) | AVENIDA | FERRAGEM | BT | 112,5KVA | AVENIDA | (KL) | 112,5KVA | ANCORAR | V3-4 | AVENIDA | (KL) | REAPROVEITAR</t>
+          <t>CABOS | ANCORAR | 3x336AN | 112,5KVA | RAMAIS | 58M | B1F | BF-A | CABOS | ANCORAR | BT | (DCIM) | MT | TX16 | AV. | 1x3x120(70)AX | 4 | 3x70AX(5AZN) | BT | C12X300112,5KVACE1112,5KVAIP | SMTG112,5KVAL1(2) | 112,5KVA | (KL) | CALÇADA | 112,5KVA | CAMINHÃO | CLANDESTINOS: | ANCORAR | 3x336AN | (DCIM) | 112,5KVA | 3x336AN | BT | 112,5KVA | AVENIDA | (KL) | ANCORAR | FERRAGEM | AVENIDA | (DCIM)</t>
         </is>
       </c>
       <c r="I8" s="4" t="n">
@@ -894,7 +902,7 @@
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>V4-5 | BT | 1x3x120(70)AX | MT | 3x70AX(5AZN) | 35.91M | 35.79M | CABOS | ANCORAR | 3x336AN | 112,5KVA | P4-30 | RAMAIS | B1F | CABOS | ANCORAR | (DCIM) | P5 | BM</t>
+          <t>1x3x120(70)AX | BT | 3x70AX(5AZN) | MT | 35.91M | 35.79M</t>
         </is>
       </c>
       <c r="I9" s="3" t="n">
@@ -931,27 +939,19 @@
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>CONCRETO</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>12m</t>
-        </is>
-      </c>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>P31 | LC | 11M | 11M | BF-A | BT | BF-A | AV. | (DCIM) | V3-4 | ANCORAR | BT | QX10 | TX10 | RAMAL | CABOS | MT | 112,5KVA | 112,5KVA | 112,5KVA | B1F | 1x3x120(70)AX | V2-3 | C12X300112,5KVACE1112,5KVAIP | RAMAIS | 3x70AX(5AZN) | SMTG112,5KVAL1(2) | 112,5KVA | BT | 3x336AN | 1x3x120(70)AX | ANCORAR | MT | CABOS | 3x70AX(5AZN)</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
+          <t>LC | 11M | BT | 11M | BF-A | AV. | BF-A | (DCIM) | BT | ANCORAR | MT</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>CRITICO</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -981,14 +981,14 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34.92m</t>
+          <t>34.24m</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>BT | MT | 1x3x120(70)AX | V3-4 | 3x70AX(5AZN) | BT | AV. | (DCIM) | V2-3 | ANCORAR | CABOS | 1x3x120(70)AX | P31 | B1F | BT | 34.92M | 35.04M | 34.24M | RAMAIS | 3x70AX(5AZN) | 112,5KVA | MT | 34.24M | 3x336AN | FONTE | ANCORAR | LADO | CABOS | 1314 | BCU | LC | 11M | 11M | BF-A | BF-A</t>
+          <t>MT | 3x70AX(5AZN) | BT | 1x3x120(70)AX | 1x3x120(70)AX | BT | 34.24M | AV. | BT | (DCIM) | 3x70AX(5AZN) | 35.04M</t>
         </is>
       </c>
       <c r="I11" s="3" t="n">
@@ -1033,7 +1033,7 @@
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>LADO | BCU | MT | 3x70AX(5AZN) | 1314 | BT | FONTE | 1x3x120(70)AX | V2-3 | 34.24M | ETAPA | 34.24M | CONEX. | 1x3x240(120)AX | 17176276 | 17176277 | MT | BF-A | INSTALAÇÃO | 3x70AX(5AZN) | BF-A | P2 | BT | DESATIVAÇÃO | 1x3x120(70)AX | P31 | V3-4</t>
+          <t>LADO | BCU | MT | 3x70AX(5AZN) | 1314 | BT | FONTE | 1x3x120(70)AX | 34.24M | ETAPA</t>
         </is>
       </c>
       <c r="I12" s="3" t="n">
@@ -1070,27 +1070,19 @@
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>CONCRETO</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>12m</t>
-        </is>
-      </c>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>V2-3 | P31 | BT | 1x3x120(70)AX | MT | MT | LC | 3x70AX(5AZN) | BT | LADO | 11M | V3-4 | BF-A | 3x70AX(5AZN) | BT | 1x3x120(70)AX | 11M | BCU | FONTE | BF-A | AV. | 1314 | CONEX. | RAMAL | (DCIM) | QX10 | 112,5KVA | ANCORAR | TX10 | 112,5KVA | 34.24M | CABOS | 112,5KVA | 34.24M | P2 | B1F | C12X300112,5KVACE1112,5KVAIP | RAMAIS</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
+          <t>BT | 1x3x120(70)AX | MT | MT | LC | BT | 3x70AX(5AZN) | 11M</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>CRITICO</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">

--- a/output_excel/17176277.xlsx
+++ b/output_excel/17176277.xlsx
@@ -470,20 +470,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="55" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="55" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -509,35 +512,50 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Rua / Avenida</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Ancoragem</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Lado Forte</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Metragem</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Altura Poste</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Informações</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Confiança</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Corrigido IA</t>
         </is>
@@ -562,27 +580,30 @@
           <t>V7-8</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>38.08m</t>
-        </is>
-      </c>
+      <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>1x3x120(70)AX | BT | 3x70AX(5AZN) | MT | 38.08M | 240.23M</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="n">
+          <t>240.23m</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>BT MT 1x3x120(70)AX 3x70AX(5AZN) | 240.23M 38.08M | 3x70AX(5AZN) 30.74M 30.74M | 1 JUQ CONEX. 1 6 2 V1-3 3 (DCIM) | 1 1 BT JUQ CONEX. CONEX. 1 1 6 0 2 V1-3 2 V1-3 1 2 0 0 (DCIM) (DCIM) | V7-8 | MT | 2 1 TX10 QX10 2 V1-3 2 V1-3 20M 3M</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -608,30 +629,33 @@
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>CONCRETO</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>12m</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>FERRAGEM | (DCIM) | DG | 20M | 3M | 6 | BF-A | 1 | 3 | CONEX. | (DCIM) | Q/R | BF-A | 1 | BF-A | 5M | BT | BF-A | MT | 0 | BF-A | 1 | 2 | DG | CONEX. | 0 | (DCIM) | Q/R | 1 | 1x3x120(70)AX | BF-A | 6 | 1 | 1 | 0 | CONEX. | (DCIM) | BT | 1 | TX10 | 3x70AX(5AZN) | QX16 | QX10 | 2 | 1 | SMTG112,5KVAL1(1) | C12X300112,5KVACEAFS112,5KVA1AF(1)112,5KVAIP | CONEX. | 1</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>C12X300112,5KVACEAFS112,5KVA1AF(1)112,5KVAIP SMTG112,5KVAL1(1) | C12X300112,5KVACEAFS112,5KVA1AF(1)112,5KVAIP SMTG112,5KVAL1(1) | (DCIM) CARGA | DG 1 1 7 P7x | V7-8 | BT MT 1x3x120(70)AX 3x70AX(5AZN) | V6-7 BT 1x3x120(70)AX</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -656,27 +680,30 @@
           <t>V6-7</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>30.74m</t>
-        </is>
-      </c>
+      <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>MT | 3x70AX(5AZN) | BT | 1x3x120(70)AX | 30.74M</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="n">
+          <t>30.74m</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>3x70AX(5AZN) 30.74M 30.74M | MT | 3x70AX(5AZN) 33.59M 33.59M | BT MT 1x3x120(70)AX 3x70AX(5AZN) | L5 2 V1-3 1 QX16 2 V1-3 5M | 240.23M 38.08M | 2 1 TX10 QX10 2 V1-3 2 V1-3 20M 3M | MT</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -702,30 +729,33 @@
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>CONCRETO</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>12m</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>DG | 5M | (DCIM) | BF-A | FERRAGEM | QX16 | BT | FERRAGEM | 3M | (DCIM) | 1 | MT | BF-A | BF-A | 1x3x120(70)AX | 20M | BF-A | 3x70AX(5AZN) | L5 | QX10 | TX10 | 1 | 2 | 4M | C12X300112,5KVACEAFS112,5KVA1AF(1)112,5KVAIP | 25M</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>C12X300112,5KVACEAFS112,5KVA1AF(1)112,5KVAIP SMTG112,5KVAL1(1) | C12X300112,5KVACEAFS112,5KVA1AF(1)112,5KVAIP SMTG112,5KVAL1(1) | DG 1 1 7 P7x | CARGA (DCIM) | V6-7 BT 1x3x120(70)AX | (DCIM) CARGA | LC P5 P6</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -750,27 +780,30 @@
           <t>V5-6</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>33.59m</t>
-        </is>
-      </c>
+      <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1x3x120(70)AX | BT | 3x70AX(5AZN) | MT | GD | 33.59M | 33.59M</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="n">
+          <t>33.59m</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>3x70AX(5AZN) 33.59M 33.59M | MT | 3x70AX(5AZN) 30.74M 30.74M | 35.79M 35.91M | 1 2 QX10 QX16 2 V1-3 2 V1-3 4M 25M | V5-6 BT 1x3x120(70)AX | 2 RAMAL</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -796,30 +829,33 @@
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>CONCRETO</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>10m</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>BM | ANCORAR | CAMINHÃO | (KL) | CALÇADA | 112,5KVA | 112,5KVA | BT | 566993 | (KL) | AVENIDA | 112,5KVA | FERRAGEM | MV | GD | CLANDESTINOS: | LC | AVENIDA | 3x336AN | 175ET005296879 | RAMAL | (DCIM) | 2 | ANCORAR | 25M | BF-A | 112,5KVA | AVENIDA | QX16 | BT | MT | 2 | 3x336AN | (KL) | 75KVA | 4M | BF-A | QX10 | ANCORAR | 1 | ANCORAR | 1x3x120(70)AX | 3x70AX(5AZN) | 13200 | C10x600,B1M,M3F</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>12m</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>C12X300112,5KVACEAFS112,5KVA1AF(1)112,5KVAIP SMTG112,5KVAL1(1) | SMTG112,5KVAL1(2) C12X300112,5KVACE1112,5KVAIP | C12X600112,5KVACE-SH112,5KVAET4A112,5KVAIP SMTR112,5KVAL1(2) | C12X300112,5KVACEAFS112,5KVA1AF(1)112,5KVAIP SMTG112,5KVAL1(1) | CAMINHÃO | GD</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -845,30 +881,33 @@
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>CONCRETO</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>12m</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>CABOS | ANCORAR | 3x336AN | 112,5KVA | RAMAIS | 58M | B1F | BF-A | CABOS | ANCORAR | BT | (DCIM) | MT | TX16 | AV. | 1x3x120(70)AX | 4 | 3x70AX(5AZN) | BT | C12X300112,5KVACE1112,5KVAIP | SMTG112,5KVAL1(2) | 112,5KVA | (KL) | CALÇADA | 112,5KVA | CAMINHÃO | CLANDESTINOS: | ANCORAR | 3x336AN | (DCIM) | 112,5KVA | 3x336AN | BT | 112,5KVA | AVENIDA | (KL) | ANCORAR | FERRAGEM | AVENIDA | (DCIM)</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>SMTG112,5KVAL1(2) C12X300112,5KVACE1112,5KVAIP | SMTG112,5KVAL1(2) C12X300112,5KVACE1112,5KVAIP | P4-30 | C12X600112,5KVACE-SH112,5KVAET4A112,5KVAIP SMTR112,5KVAL1(2) | B1F RAMAIS 112,5KVA | V4-5</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -893,27 +932,30 @@
           <t>V4-5</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>35.91m</t>
-        </is>
-      </c>
+      <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1x3x120(70)AX | BT | 3x70AX(5AZN) | MT | 35.91M | 35.79M</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="n">
+          <t>35.79m</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>MT BT 1x3x120(70)AX 3x70AX(5AZN) | 35.79M 35.91M | 3x70AX(5AZN) 34.92M 35.04M | 4 TX16 2 V1-3 58M | V4-5 | 3x70AX(5AZN) 33.59M 33.59M | 2 V1-3 12M 175ET005296879 566993</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="M9" s="3" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -941,20 +983,31 @@
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>LC | 11M | BT | 11M | BF-A | AV. | BF-A | (DCIM) | BT | ANCORAR | MT</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>12m</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>SMTG112,5KVAL1(2) C12X300112,5KVACE1112,5KVAIP | SMTG112,5KVAL1(2) C12X300112,5KVACE1112,5KVAIP | SMFL112,5KVAL1(2) C12X300112,5KVACE1112,5KVAIP | LC P5 P31 | BT AV. | V3-4 BT 1x3x120(70)AX | 2 RAMAL</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -979,27 +1032,30 @@
           <t>V3-4</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>34.24m</t>
-        </is>
-      </c>
+      <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>MT | 3x70AX(5AZN) | BT | 1x3x120(70)AX | 1x3x120(70)AX | BT | 34.24M | AV. | BT | (DCIM) | 3x70AX(5AZN) | 35.04M</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="n">
+          <t>34.92m</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>3x70AX(5AZN) 34.92M 35.04M | MT | MT BT 1x3x120(70)AX 3x70AX(5AZN) | 34.24M 34.24M | 1 1 TX10 QX10 2 V1-3 2 V1-3 11M 11M | 2 RAMAL | MT BT 1x3x120(70)AX 3x70AX(5AZN) | 4 TX16 2 V1-3 58M</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="M11" s="3" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1024,27 +1080,30 @@
           <t>V2-3</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>34.24m</t>
-        </is>
-      </c>
+      <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>LADO | BCU | MT | 3x70AX(5AZN) | 1314 | BT | FONTE | 1x3x120(70)AX | 34.24M | ETAPA</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="n">
+          <t>34.24m</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>MT BT 1x3x120(70)AX 3x70AX(5AZN) | 34.24M 34.24M | 3x70AX(5AZN) 34.92M 35.04M | MT | 2 RAMAL | 1 1 TX10 QX10 2 V1-3 2 V1-3 11M 11M | LADO BCU 1314 FONTE | V2-3</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="M12" s="3" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1072,20 +1131,31 @@
       <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>BT | 1x3x120(70)AX | MT | MT | LC | BT | 3x70AX(5AZN) | 11M</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>12m</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>SMTG112,5KVAL1(2) C12X300112,5KVACE1112,5KVAIP | SMFL112,5KVAL1(2) C12X300112,5KVACE1112,5KVAIP | SMTG112,5KVAL1(2) C12X300112,5KVACE1112,5KVAIP | V2-3 | LC P5 P31 | MT BT 1x3x120(70)AX 3x70AX(5AZN) | V3-4 BT 1x3x120(70)AX | BT AV.</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
